--- a/astro-site/public/dl/kit-tareas/05-tareas-semanales-mensuales.xlsx
+++ b/astro-site/public/dl/kit-tareas/05-tareas-semanales-mensuales.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Limpieza Semanal" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="FIFO Semanal" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Mantenimiento Mensual" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Limpieza Semanal" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FIFO Semanal" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mantenimiento Mensual" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="1" name="_xlnm.Print_Area">'Limpieza Semanal'!$A$1:$G$34</definedName>
-    <definedName localSheetId="2" name="_xlnm.Print_Area">'FIFO Semanal'!$A$1:$G$33</definedName>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Mantenimiento Mensual'!$A$1:$G$30</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Limpieza Semanal'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Limpieza Semanal'!$A$1:$G$34</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'FIFO Semanal'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'FIFO Semanal'!$A$1:$G$33</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Mantenimiento Mensual'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Mantenimiento Mensual'!$A$1:$G$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -135,7 +138,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -157,63 +160,122 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="30">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="6" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -573,15 +635,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B10"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -589,6 +652,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -596,9 +660,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -620,9 +682,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" t="inlineStr"/>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -630,8 +690,33 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -640,18 +725,18 @@
   <sheetPr>
     <tabColor rgb="004CAF50"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -668,10 +753,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -696,7 +782,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -711,18 +797,16 @@
           <t xml:space="preserve">  COCINA — Limpieza profunda</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="27" t="n"/>
+      <c r="C5" s="27" t="n"/>
+      <c r="D5" s="27" t="n"/>
+      <c r="E5" s="27" t="n"/>
+      <c r="F5" s="27" t="n"/>
+      <c r="G5" s="28" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="29" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -748,10 +832,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="29" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -777,10 +859,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="29" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -806,10 +886,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="29" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -835,10 +913,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="29" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -864,10 +940,8 @@
       <c r="G10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="29" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -893,10 +967,8 @@
       <c r="G11" s="15" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="29" t="n">
+        <v>7</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
@@ -922,10 +994,8 @@
       <c r="G12" s="15" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="29" t="n">
+        <v>8</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -951,10 +1021,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="29" t="n">
+        <v>9</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -979,24 +1047,23 @@
       <c r="F14" s="14" t="n"/>
       <c r="G14" s="15" t="n"/>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  SALA Y BARRA</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="8" t="n"/>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="8" t="n"/>
+      <c r="B16" s="27" t="n"/>
+      <c r="C16" s="27" t="n"/>
+      <c r="D16" s="27" t="n"/>
+      <c r="E16" s="27" t="n"/>
+      <c r="F16" s="27" t="n"/>
+      <c r="G16" s="28" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="29" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -1022,10 +1089,8 @@
       <c r="G17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="29" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -1051,10 +1116,8 @@
       <c r="G18" s="15" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="29" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -1080,10 +1143,8 @@
       <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="29" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -1109,10 +1170,8 @@
       <c r="G20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="29" t="n">
+        <v>14</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -1137,24 +1196,23 @@
       <c r="F21" s="14" t="n"/>
       <c r="G21" s="15" t="n"/>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  BAÑOS Y GENERAL</t>
         </is>
       </c>
-      <c r="B23" s="8" t="n"/>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="n"/>
-      <c r="G23" s="8" t="n"/>
+      <c r="B23" s="27" t="n"/>
+      <c r="C23" s="27" t="n"/>
+      <c r="D23" s="27" t="n"/>
+      <c r="E23" s="27" t="n"/>
+      <c r="F23" s="27" t="n"/>
+      <c r="G23" s="28" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="29" t="n">
+        <v>15</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
@@ -1180,10 +1238,8 @@
       <c r="G24" s="15" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="29" t="n">
+        <v>16</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
@@ -1209,10 +1265,8 @@
       <c r="G25" s="15" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="29" t="n">
+        <v>17</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
@@ -1238,10 +1292,8 @@
       <c r="G26" s="15" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A27" s="29" t="n">
+        <v>18</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
@@ -1266,6 +1318,8 @@
       <c r="F27" s="14" t="n"/>
       <c r="G27" s="15" t="n"/>
     </row>
+    <row r="28"/>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
         <is>
@@ -1274,17 +1328,19 @@
       </c>
       <c r="D30" s="16">
         <f>COUNTIF(F5:F28,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F30" s="16" t="n">
-        <v>18</v>
-      </c>
-    </row>
+      <c r="F30" s="16">
+        <f>COUNTIF(B5:B28,"?*")</f>
+        <v>18.0</v>
+      </c>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
         <is>
@@ -1292,13 +1348,17 @@
         </is>
       </c>
       <c r="B32" s="15" t="n"/>
+      <c r="C32" s="27" t="n"/>
+      <c r="D32" s="28" t="n"/>
       <c r="E32" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F32" s="15" t="n"/>
-    </row>
+      <c r="G32" s="28" t="n"/>
+    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="18" t="inlineStr">
         <is>
@@ -1317,13 +1377,26 @@
     <mergeCell ref="A23:G23"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G28">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F11 F12 F13 F14 F17 F18 F19 F20 F21 F24 F25 F26 F27" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F14 F17 F18 F19 F20 F21 F24 F25 F26 F27 F28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1332,18 +1405,18 @@
   <sheetPr>
     <tabColor rgb="00FF9800"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1360,10 +1433,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1388,7 +1462,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1403,18 +1477,16 @@
           <t xml:space="preserve">  CÁMARA REFRIGERACIÓN 1</t>
         </is>
       </c>
-      <c r="B5" s="15" t="n"/>
-      <c r="C5" s="15" t="n"/>
-      <c r="D5" s="15" t="n"/>
-      <c r="E5" s="15" t="n"/>
-      <c r="F5" s="15" t="n"/>
-      <c r="G5" s="15" t="n"/>
+      <c r="B5" s="27" t="n"/>
+      <c r="C5" s="27" t="n"/>
+      <c r="D5" s="27" t="n"/>
+      <c r="E5" s="27" t="n"/>
+      <c r="F5" s="27" t="n"/>
+      <c r="G5" s="28" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="29" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -1440,10 +1512,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="29" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -1469,10 +1539,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="29" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -1498,10 +1566,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="29" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -1526,24 +1592,23 @@
       <c r="F9" s="14" t="n"/>
       <c r="G9" s="15" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  CÁMARA REFRIGERACIÓN 2</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="15" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="15" t="n"/>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="B11" s="27" t="n"/>
+      <c r="C11" s="27" t="n"/>
+      <c r="D11" s="27" t="n"/>
+      <c r="E11" s="27" t="n"/>
+      <c r="F11" s="27" t="n"/>
+      <c r="G11" s="28" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="29" t="n">
+        <v>5</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
@@ -1569,10 +1634,8 @@
       <c r="G12" s="15" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="29" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -1598,10 +1661,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="29" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -1626,24 +1687,23 @@
       <c r="F14" s="14" t="n"/>
       <c r="G14" s="15" t="n"/>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  CONGELADOR</t>
         </is>
       </c>
-      <c r="B16" s="15" t="n"/>
-      <c r="C16" s="15" t="n"/>
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="15" t="n"/>
-      <c r="F16" s="15" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="B16" s="27" t="n"/>
+      <c r="C16" s="27" t="n"/>
+      <c r="D16" s="27" t="n"/>
+      <c r="E16" s="27" t="n"/>
+      <c r="F16" s="27" t="n"/>
+      <c r="G16" s="28" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="29" t="n">
+        <v>8</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -1669,10 +1729,8 @@
       <c r="G17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="29" t="n">
+        <v>9</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -1698,10 +1756,8 @@
       <c r="G18" s="15" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="29" t="n">
+        <v>10</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -1727,10 +1783,8 @@
       <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="29" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -1755,24 +1809,23 @@
       <c r="F20" s="14" t="n"/>
       <c r="G20" s="15" t="n"/>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  ALMACÉN SECO</t>
         </is>
       </c>
-      <c r="B22" s="15" t="n"/>
-      <c r="C22" s="15" t="n"/>
-      <c r="D22" s="15" t="n"/>
-      <c r="E22" s="15" t="n"/>
-      <c r="F22" s="15" t="n"/>
-      <c r="G22" s="15" t="n"/>
+      <c r="B22" s="27" t="n"/>
+      <c r="C22" s="27" t="n"/>
+      <c r="D22" s="27" t="n"/>
+      <c r="E22" s="27" t="n"/>
+      <c r="F22" s="27" t="n"/>
+      <c r="G22" s="28" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="29" t="n">
+        <v>12</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -1798,10 +1851,8 @@
       <c r="G23" s="15" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="29" t="n">
+        <v>13</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
@@ -1827,10 +1878,8 @@
       <c r="G24" s="15" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="29" t="n">
+        <v>14</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
@@ -1856,10 +1905,8 @@
       <c r="G25" s="15" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="29" t="n">
+        <v>15</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
@@ -1884,6 +1931,8 @@
       <c r="F26" s="14" t="n"/>
       <c r="G26" s="15" t="n"/>
     </row>
+    <row r="27"/>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
@@ -1892,17 +1941,19 @@
       </c>
       <c r="D29" s="16">
         <f>COUNTIF(F5:F27,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E29" s="17" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F29" s="16" t="n">
-        <v>15</v>
-      </c>
-    </row>
+      <c r="F29" s="16">
+        <f>COUNTIF(B5:B27,"?*")</f>
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
         <is>
@@ -1910,13 +1961,17 @@
         </is>
       </c>
       <c r="B31" s="15" t="n"/>
+      <c r="C31" s="27" t="n"/>
+      <c r="D31" s="28" t="n"/>
       <c r="E31" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F31" s="15" t="n"/>
-    </row>
+      <c r="G31" s="28" t="n"/>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="18" t="inlineStr">
         <is>
@@ -1936,13 +1991,26 @@
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A22:G22"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G27">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F12 F13 F14 F17 F18 F19 F20 F23 F24 F25 F26" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F17 F18 F19 F20 F23 F24 F25 F26 F27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1951,18 +2019,18 @@
   <sheetPr>
     <tabColor rgb="00795548"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1979,10 +2047,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -2007,7 +2076,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -2022,18 +2091,16 @@
           <t xml:space="preserve">  EQUIPOS DE COCINA</t>
         </is>
       </c>
-      <c r="B5" s="15" t="n"/>
-      <c r="C5" s="15" t="n"/>
-      <c r="D5" s="15" t="n"/>
-      <c r="E5" s="15" t="n"/>
-      <c r="F5" s="15" t="n"/>
-      <c r="G5" s="15" t="n"/>
+      <c r="B5" s="27" t="n"/>
+      <c r="C5" s="27" t="n"/>
+      <c r="D5" s="27" t="n"/>
+      <c r="E5" s="27" t="n"/>
+      <c r="F5" s="27" t="n"/>
+      <c r="G5" s="28" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="29" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -2059,10 +2126,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="29" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -2088,10 +2153,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="29" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -2117,10 +2180,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="29" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -2146,10 +2207,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="29" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -2175,10 +2234,8 @@
       <c r="G10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="29" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -2203,24 +2260,23 @@
       <c r="F11" s="14" t="n"/>
       <c r="G11" s="15" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  SALA Y BARRA</t>
         </is>
       </c>
-      <c r="B13" s="22" t="n"/>
-      <c r="C13" s="22" t="n"/>
-      <c r="D13" s="22" t="n"/>
-      <c r="E13" s="22" t="n"/>
-      <c r="F13" s="22" t="n"/>
-      <c r="G13" s="22" t="n"/>
+      <c r="B13" s="27" t="n"/>
+      <c r="C13" s="27" t="n"/>
+      <c r="D13" s="27" t="n"/>
+      <c r="E13" s="27" t="n"/>
+      <c r="F13" s="27" t="n"/>
+      <c r="G13" s="28" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="29" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -2246,10 +2302,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="29" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -2275,10 +2329,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="29" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -2304,10 +2356,8 @@
       <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="29" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -2332,24 +2382,23 @@
       <c r="F17" s="14" t="n"/>
       <c r="G17" s="15" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  SEGURIDAD</t>
         </is>
       </c>
-      <c r="B19" s="25" t="n"/>
-      <c r="C19" s="25" t="n"/>
-      <c r="D19" s="25" t="n"/>
-      <c r="E19" s="25" t="n"/>
-      <c r="F19" s="25" t="n"/>
-      <c r="G19" s="25" t="n"/>
+      <c r="B19" s="27" t="n"/>
+      <c r="C19" s="27" t="n"/>
+      <c r="D19" s="27" t="n"/>
+      <c r="E19" s="27" t="n"/>
+      <c r="F19" s="27" t="n"/>
+      <c r="G19" s="28" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="29" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -2375,10 +2424,8 @@
       <c r="G20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="29" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -2404,10 +2451,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="29" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
@@ -2433,10 +2478,8 @@
       <c r="G22" s="15" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="29" t="n">
+        <v>14</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -2461,6 +2504,8 @@
       <c r="F23" s="14" t="n"/>
       <c r="G23" s="15" t="n"/>
     </row>
+    <row r="24"/>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
         <is>
@@ -2469,17 +2514,19 @@
       </c>
       <c r="D26" s="16">
         <f>COUNTIF(F5:F24,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F26" s="16" t="n">
-        <v>14</v>
-      </c>
-    </row>
+      <c r="F26" s="16">
+        <f>COUNTIF(B5:B24,"?*")</f>
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
         <is>
@@ -2487,13 +2534,17 @@
         </is>
       </c>
       <c r="B28" s="15" t="n"/>
+      <c r="C28" s="27" t="n"/>
+      <c r="D28" s="28" t="n"/>
       <c r="E28" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F28" s="15" t="n"/>
-    </row>
+      <c r="G28" s="28" t="n"/>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="18" t="inlineStr">
         <is>
@@ -2504,20 +2555,33 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A26:C26"/>
-    <mergeCell ref="F28:G28"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="F28:G28"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A19:G19"/>
     <mergeCell ref="B28:D28"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G24">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F20 F21 F22 F23" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F20 F21 F22 F23 F24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas/05-tareas-semanales-mensuales.xlsx
+++ b/astro-site/public/dl/kit-tareas/05-tareas-semanales-mensuales.xlsx
@@ -11,14 +11,18 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Limpieza Semanal" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FIFO Semanal" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mantenimiento Mensual" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trimestral y Anual" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$45</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Limpieza Semanal'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Limpieza Semanal'!$A$1:$G$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Limpieza Semanal'!$A$1:$G$38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'FIFO Semanal'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'FIFO Semanal'!$A$1:$G$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'FIFO Semanal'!$A$1:$G$49</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Mantenimiento Mensual'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Mantenimiento Mensual'!$A$1:$G$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Mantenimiento Mensual'!$A$1:$G$35</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Trimestral y Anual'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Trimestral y Anual'!$A$1:$G$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -99,8 +103,22 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -135,6 +153,16 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F5F5F5"/>
         <bgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F2FD"/>
       </patternFill>
     </fill>
   </fills>
@@ -208,7 +236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -260,6 +288,77 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -637,72 +736,220 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>Tareas Semanales y Mensuales — Restaurante Casual</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>Cómo usar estas plantillas</t>
         </is>
       </c>
     </row>
     <row r="5"/>
-    <row r="6">
-      <c r="B6" s="3" t="inlineStr">
+    <row r="6" ht="16" customHeight="1">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>▸ Imprime la hoja semanal cada lunes y la mensual cada día 1</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="3" t="inlineStr">
+    <row r="7" ht="16" customHeight="1">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>▸ Asigna cada tarea a un responsable con fecha límite</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>▸ Archiva las hojas firmadas junto con los registros APPCC</t>
+    <row r="8" ht="32" customHeight="1">
+      <c r="B8" s="32" t="inlineStr">
+        <is>
+          <t>▸ Archiva las hojas firmadas junto a tus registros de higiene: si tienes el Pack APPCC, con sus hojas; si no, con los tuyos</t>
         </is>
       </c>
     </row>
     <row r="9"/>
-    <row r="10">
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes · AI Chef Pro · aichef.pro</t>
+    <row r="10" ht="18" customHeight="1">
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>Trimestral, anual y vida útil en congelación</t>
         </is>
       </c>
     </row>
     <row r="11"/>
-    <row r="12">
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas · info@aichef.pro</t>
+    <row r="12" ht="48" customHeight="1">
+      <c r="B12" s="32" t="inlineStr">
+        <is>
+          <t>▸ La hoja «Trimestral y Anual» recoge el mantenimiento que se CONTRATA y que se pide en una inspección: DDD, conductos de extracción, extintores y BIE, instalación de gas, legionela, seguro y facturación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="B13" s="32" t="inlineStr">
+        <is>
+          <t>▸ Anota el número de parte en la columna verde y firma cuando la empresa haya venido; la última tarea de la hoja es apuntar la fecha de la próxima revisión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="B14" s="32" t="inlineStr">
+        <is>
+          <t>▸ Al pie de «FIFO Semanal» tienes una tabla editable de vida útil en congelación por familia: una regla única para todo el congelador o tira producto bueno o valida producto pasado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16" ht="18" customHeight="1">
+      <c r="B16" s="31" t="inlineStr">
+        <is>
+          <t>Cómo cuenta el contador</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18" ht="32" customHeight="1">
+      <c r="B18" s="32" t="inlineStr">
+        <is>
+          <t>▸ Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="B19" s="32" t="inlineStr">
+        <is>
+          <t>▸ «N/A» = no aplica en tu local: esa tarea SALE del total (no la borres, márcala N/A). «—» = no hecha: sigue contando como pendiente y baja el porcentaje, que es de lo que se trata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="B20" s="32" t="inlineStr">
+        <is>
+          <t>▸ El denominador cuenta las tareas escritas en la columna «Tarea», no un número fijo: si añades o borras tareas, el total se ajusta solo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="B22" s="31" t="inlineStr">
+        <is>
+          <t>Filas libres</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="B24" s="32" t="inlineStr">
+        <is>
+          <t>▸ Al final de cada tabla hay 5 filas verdes libres DENTRO del rango que cuenta el contador: escribe ahí tus tareas propias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="B25" s="32" t="inlineStr">
+        <is>
+          <t>▸ Si necesitas más, inserta filas DENTRO de la tabla (clic derecho → Insertar), nunca por debajo de la última: lo que se escriba fuera del rango no lo cuenta nadie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="B27" s="31" t="inlineStr">
+        <is>
+          <t>Protección de la hoja</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="B29" s="32" t="inlineStr">
+        <is>
+          <t>▸ Las hojas con fórmulas van protegidas SIN contraseña: las celdas de entrada (las verdes) están desbloqueadas y los cálculos no se pisan por accidente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="B30" s="32" t="inlineStr">
+        <is>
+          <t>▸ Puedes insertar y borrar filas con la protección puesta. Para cambiar la estructura: Revisar → Desproteger hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="B32" s="31" t="inlineStr">
+        <is>
+          <t>Se conecta con</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="B34" s="32" t="inlineStr">
+        <is>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día (accesos, luces, clima, terraza).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="B35" s="32" t="inlineStr">
+        <is>
+          <t>▸ 01-apertura-cierre.xlsx — el mismo día con el DETALLE por área (cocina, sala, barra).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="B36" s="32" t="inlineStr">
+        <is>
+          <t>▸ 09-apertura-cierre-caja.xlsx — la CAJA: fondo, recuento por denominaciones, Z del TPV y descuadre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="B37" s="32" t="inlineStr">
+        <is>
+          <t>▸ Orden de uso: local → áreas → caja. No se duplican: cada uno cubre un nivel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="B38" s="32" t="inlineStr">
+        <is>
+          <t>▸ Estás en 05-tareas-semanales-mensuales.xlsx: lo que NO es diario (semanal, mensual, trimestral y anual). El día a día está en 08-apertura-cierre-negocio.xlsx y 01-apertura-cierre.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="31" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="35" customHeight="1">
+      <c r="B42" s="31" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="31" t="inlineStr">
+        <is>
+          <t>Contacto: info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="31" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -727,7 +974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -749,7 +996,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable turno: _________________________</t>
+          <t>Semana del ___/___/______ al ___/___/______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -777,7 +1024,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Día</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -792,598 +1039,659 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  COCINA — Limpieza profunda</t>
         </is>
       </c>
-      <c r="B5" s="27" t="n"/>
-      <c r="C5" s="27" t="n"/>
-      <c r="D5" s="27" t="n"/>
-      <c r="E5" s="27" t="n"/>
-      <c r="F5" s="27" t="n"/>
-      <c r="G5" s="28" t="n"/>
+      <c r="B5" s="34" t="n"/>
+      <c r="C5" s="34" t="n"/>
+      <c r="D5" s="34" t="n"/>
+      <c r="E5" s="34" t="n"/>
+      <c r="F5" s="34" t="n"/>
+      <c r="G5" s="35" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="n">
+      <c r="A6" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>Limpiar interior de cámaras frigoríficas</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="38" t="inlineStr">
         <is>
           <t>Limpieza</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="39" t="inlineStr">
         <is>
           <t>Equipo cocina</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="39" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="F6" s="40" t="n"/>
+      <c r="G6" s="41" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="n">
+      <c r="A7" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>Desmontar y limpiar quemadores de fogones</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="38" t="inlineStr">
         <is>
           <t>Limpieza</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="39" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="39" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="40" t="n"/>
+      <c r="G7" s="41" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="n">
+      <c r="A8" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>Limpiar horno por dentro (pirolisis o manual)</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="38" t="inlineStr">
         <is>
           <t>Limpieza</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="39" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="39" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="F8" s="40" t="n"/>
+      <c r="G8" s="41" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="n">
+      <c r="A9" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t>Desmontar y limpiar filtros de campana</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="38" t="inlineStr">
         <is>
           <t>Limpieza</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="39" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="39" t="inlineStr">
         <is>
           <t>Miércoles</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="40" t="n"/>
+      <c r="G9" s="41" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="n">
+      <c r="A10" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="37" t="inlineStr">
         <is>
           <t>Limpiar freidora: vaciar, desengrasante, aclarar</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="38" t="inlineStr">
         <is>
           <t>Limpieza</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="39" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="39" t="inlineStr">
         <is>
           <t>Miércoles</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
+      <c r="F10" s="40" t="n"/>
+      <c r="G10" s="41" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="n">
+      <c r="A11" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="37" t="inlineStr">
         <is>
           <t>Limpiar interior de microondas y salamandra</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="38" t="inlineStr">
         <is>
           <t>Limpieza</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="39" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="39" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="F11" s="40" t="n"/>
+      <c r="G11" s="41" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="n">
+      <c r="A12" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>Limpiar rejillas de ventilación</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="38" t="inlineStr">
         <is>
           <t>Limpieza</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="39" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="39" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="15" t="n"/>
+      <c r="F12" s="40" t="n"/>
+      <c r="G12" s="41" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="n">
+      <c r="A13" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t>Limpiar detrás de equipos (mover si es posible)</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="38" t="inlineStr">
         <is>
           <t>Limpieza</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="39" t="inlineStr">
         <is>
           <t>Equipo cocina</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="39" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="F13" s="40" t="n"/>
+      <c r="G13" s="41" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="29" t="n">
+      <c r="A14" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Descalcificar lavavajillas</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="B14" s="37" t="inlineStr">
+        <is>
+          <t>Limpiar filtros, brazos de lavado y cuba del lavavajillas</t>
+        </is>
+      </c>
+      <c r="C14" s="38" t="inlineStr">
         <is>
           <t>Limpieza</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="39" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="39" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
-    </row>
-    <row r="15"/>
+      <c r="F14" s="40" t="n"/>
+      <c r="G14" s="41" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="42" t="n"/>
+      <c r="B15" s="42" t="n"/>
+      <c r="C15" s="42" t="n"/>
+      <c r="D15" s="42" t="n"/>
+      <c r="E15" s="42" t="n"/>
+      <c r="F15" s="42" t="n"/>
+      <c r="G15" s="42" t="n"/>
+    </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  SALA Y BARRA</t>
         </is>
       </c>
-      <c r="B16" s="27" t="n"/>
-      <c r="C16" s="27" t="n"/>
-      <c r="D16" s="27" t="n"/>
-      <c r="E16" s="27" t="n"/>
-      <c r="F16" s="27" t="n"/>
-      <c r="G16" s="28" t="n"/>
+      <c r="B16" s="34" t="n"/>
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="34" t="n"/>
+      <c r="E16" s="34" t="n"/>
+      <c r="F16" s="34" t="n"/>
+      <c r="G16" s="35" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="29" t="n">
+      <c r="A17" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="37" t="inlineStr">
         <is>
           <t>Limpiar cristales y espejos</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="38" t="inlineStr">
         <is>
           <t>Limpieza</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="39" t="inlineStr">
         <is>
           <t>Personal limpieza</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="39" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="F17" s="40" t="n"/>
+      <c r="G17" s="41" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="29" t="n">
+      <c r="A18" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>Limpiar sillas por debajo y patas</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="38" t="inlineStr">
         <is>
           <t>Limpieza</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="39" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="39" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="15" t="n"/>
+      <c r="F18" s="40" t="n"/>
+      <c r="G18" s="41" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="29" t="n">
+      <c r="A19" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Limpiar vitrina de barra por dentro</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="38" t="inlineStr">
         <is>
           <t>Limpieza</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="39" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="39" t="inlineStr">
         <is>
           <t>Miércoles</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="15" t="n"/>
+      <c r="F19" s="40" t="n"/>
+      <c r="G19" s="41" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="n">
+      <c r="A20" s="36" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>Descalcificar máquina de café</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="B20" s="37" t="inlineStr">
+        <is>
+          <t>Limpieza química del grupo con detergente (backflush) + remojo de portafiltros, filtros y duchas</t>
+        </is>
+      </c>
+      <c r="C20" s="38" t="inlineStr">
         <is>
           <t>Limpieza</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="39" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="39" t="inlineStr">
         <is>
           <t>Miércoles</t>
         </is>
       </c>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="F20" s="40" t="n"/>
+      <c r="G20" s="41" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="29" t="n">
+      <c r="A21" s="36" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="37" t="inlineStr">
         <is>
           <t>Limpiar conductos de cerveza de barril</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C21" s="38" t="inlineStr">
         <is>
           <t>Limpieza</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="39" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="39" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="15" t="n"/>
-    </row>
-    <row r="22"/>
+      <c r="F21" s="40" t="n"/>
+      <c r="G21" s="41" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="42" t="n"/>
+      <c r="B22" s="42" t="n"/>
+      <c r="C22" s="42" t="n"/>
+      <c r="D22" s="42" t="n"/>
+      <c r="E22" s="42" t="n"/>
+      <c r="F22" s="42" t="n"/>
+      <c r="G22" s="42" t="n"/>
+    </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  BAÑOS Y GENERAL</t>
         </is>
       </c>
-      <c r="B23" s="27" t="n"/>
-      <c r="C23" s="27" t="n"/>
-      <c r="D23" s="27" t="n"/>
-      <c r="E23" s="27" t="n"/>
-      <c r="F23" s="27" t="n"/>
-      <c r="G23" s="28" t="n"/>
+      <c r="B23" s="34" t="n"/>
+      <c r="C23" s="34" t="n"/>
+      <c r="D23" s="34" t="n"/>
+      <c r="E23" s="34" t="n"/>
+      <c r="F23" s="34" t="n"/>
+      <c r="G23" s="35" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="29" t="n">
+      <c r="A24" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="37" t="inlineStr">
         <is>
           <t>Limpieza profunda de baños (azulejos, juntas)</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="38" t="inlineStr">
         <is>
           <t>Limpieza</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D24" s="39" t="inlineStr">
         <is>
           <t>Personal limpieza</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E24" s="39" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="15" t="n"/>
+      <c r="F24" s="40" t="n"/>
+      <c r="G24" s="41" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="29" t="n">
+      <c r="A25" s="36" t="n">
         <v>16</v>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="37" t="inlineStr">
         <is>
           <t>Limpiar vestuarios del personal</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" s="38" t="inlineStr">
         <is>
           <t>Limpieza</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="39" t="inlineStr">
         <is>
           <t>Personal limpieza</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E25" s="39" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="15" t="n"/>
+      <c r="F25" s="40" t="n"/>
+      <c r="G25" s="41" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="29" t="n">
+      <c r="A26" s="36" t="n">
         <v>17</v>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="37" t="inlineStr">
         <is>
           <t>Limpiar terraza a fondo (suelos, macetas)</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C26" s="38" t="inlineStr">
         <is>
           <t>Limpieza</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D26" s="39" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="E26" s="39" t="inlineStr">
         <is>
           <t>Sábado</t>
         </is>
       </c>
-      <c r="F26" s="14" t="n"/>
-      <c r="G26" s="15" t="n"/>
+      <c r="F26" s="40" t="n"/>
+      <c r="G26" s="41" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="29" t="n">
+      <c r="A27" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="37" t="inlineStr">
         <is>
           <t>Revisar y reponer productos de limpieza</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C27" s="38" t="inlineStr">
         <is>
           <t>Limpieza</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D27" s="39" t="inlineStr">
         <is>
           <t>Encargado</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E27" s="39" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
-      <c r="F27" s="14" t="n"/>
-      <c r="G27" s="15" t="n"/>
-    </row>
-    <row r="28"/>
-    <row r="29"/>
+      <c r="F27" s="40" t="n"/>
+      <c r="G27" s="41" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="43" t="n"/>
+      <c r="B28" s="44" t="n"/>
+      <c r="C28" s="38" t="n"/>
+      <c r="D28" s="39" t="n"/>
+      <c r="E28" s="39" t="n"/>
+      <c r="F28" s="40" t="n"/>
+      <c r="G28" s="41" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="43" t="n"/>
+      <c r="B29" s="44" t="n"/>
+      <c r="C29" s="38" t="n"/>
+      <c r="D29" s="39" t="n"/>
+      <c r="E29" s="39" t="n"/>
+      <c r="F29" s="40" t="n"/>
+      <c r="G29" s="41" t="n"/>
+    </row>
     <row r="30">
-      <c r="A30" s="16" t="inlineStr">
-        <is>
-          <t>Tareas completadas:</t>
-        </is>
-      </c>
-      <c r="D30" s="16">
-        <f>COUNTIF(F5:F28,"✓")</f>
-        <v>0.0</v>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="F30" s="16">
-        <f>COUNTIF(B5:B28,"?*")</f>
-        <v>18.0</v>
-      </c>
-    </row>
-    <row r="31"/>
+      <c r="A30" s="43" t="n"/>
+      <c r="B30" s="44" t="n"/>
+      <c r="C30" s="38" t="n"/>
+      <c r="D30" s="39" t="n"/>
+      <c r="E30" s="39" t="n"/>
+      <c r="F30" s="40" t="n"/>
+      <c r="G30" s="41" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="43" t="n"/>
+      <c r="B31" s="44" t="n"/>
+      <c r="C31" s="38" t="n"/>
+      <c r="D31" s="39" t="n"/>
+      <c r="E31" s="39" t="n"/>
+      <c r="F31" s="40" t="n"/>
+      <c r="G31" s="41" t="n"/>
+    </row>
     <row r="32">
-      <c r="A32" s="16" t="inlineStr">
-        <is>
-          <t>Verificado por:</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="n"/>
-      <c r="C32" s="27" t="n"/>
-      <c r="D32" s="28" t="n"/>
-      <c r="E32" s="16" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="F32" s="15" t="n"/>
-      <c r="G32" s="28" t="n"/>
+      <c r="A32" s="43" t="n"/>
+      <c r="B32" s="44" t="n"/>
+      <c r="C32" s="38" t="n"/>
+      <c r="D32" s="39" t="n"/>
+      <c r="E32" s="39" t="n"/>
+      <c r="F32" s="40" t="n"/>
+      <c r="G32" s="41" t="n"/>
     </row>
     <row r="33"/>
     <row r="34">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D34" s="16">
+        <f>COUNTIFS(B5:B32,"?*",F5:F32,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F34" s="16">
+        <f>COUNTIF(B5:B32,"?*")-COUNTIF(F5:F32,"N/A")</f>
+        <v>18.0</v>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>Verificado por:</t>
+        </is>
+      </c>
+      <c r="B36" s="45" t="n"/>
+      <c r="C36" s="27" t="n"/>
+      <c r="D36" s="28" t="n"/>
+      <c r="E36" s="16" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F36" s="45" t="n"/>
+      <c r="G36" s="28" t="n"/>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="8">
-    <mergeCell ref="F32:G32"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B32:D32"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A34:C34"/>
     <mergeCell ref="A23:G23"/>
+    <mergeCell ref="F36:G36"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="B36:D36"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G28">
+  <conditionalFormatting sqref="A5:G32">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F14 F17 F18 F19 F20 F21 F24 F25 F26 F27 F28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F14 F17 F18 F19 F20 F21 F24 F25 F26 F27 F28 F29 F30 F31 F32" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1407,7 +1715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1429,7 +1737,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable turno: _________________________</t>
+          <t>Semana del ___/___/______ al ___/___/______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1765,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Día</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -1472,532 +1780,836 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">  CÁMARA REFRIGERACIÓN 1</t>
         </is>
       </c>
-      <c r="B5" s="27" t="n"/>
-      <c r="C5" s="27" t="n"/>
-      <c r="D5" s="27" t="n"/>
-      <c r="E5" s="27" t="n"/>
-      <c r="F5" s="27" t="n"/>
-      <c r="G5" s="28" t="n"/>
+      <c r="B5" s="34" t="n"/>
+      <c r="C5" s="34" t="n"/>
+      <c r="D5" s="34" t="n"/>
+      <c r="E5" s="34" t="n"/>
+      <c r="F5" s="34" t="n"/>
+      <c r="G5" s="35" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="n">
+      <c r="A6" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>Verificar etiquetado y fechas de todas las bandejas</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="38" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="39" t="inlineStr">
         <is>
           <t>Sous Chef</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="39" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="F6" s="40" t="n"/>
+      <c r="G6" s="41" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="n">
+      <c r="A7" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>Reorganizar: producto más antiguo delante</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="38" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="39" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="39" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="40" t="n"/>
+      <c r="G7" s="41" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="n">
+      <c r="A8" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>Retirar producto caducado o sin etiquetar</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="38" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="39" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="39" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="F8" s="40" t="n"/>
+      <c r="G8" s="41" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="n">
+      <c r="A9" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t>Verificar que crudo y cocinado están separados</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="38" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="39" t="inlineStr">
         <is>
           <t>Sous Chef</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="39" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
-    </row>
-    <row r="10"/>
+      <c r="F9" s="40" t="n"/>
+      <c r="G9" s="41" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="42" t="n"/>
+      <c r="B10" s="42" t="n"/>
+      <c r="C10" s="42" t="n"/>
+      <c r="D10" s="42" t="n"/>
+      <c r="E10" s="42" t="n"/>
+      <c r="F10" s="42" t="n"/>
+      <c r="G10" s="42" t="n"/>
+    </row>
     <row r="11">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">  CÁMARA REFRIGERACIÓN 2</t>
         </is>
       </c>
-      <c r="B11" s="27" t="n"/>
-      <c r="C11" s="27" t="n"/>
-      <c r="D11" s="27" t="n"/>
-      <c r="E11" s="27" t="n"/>
-      <c r="F11" s="27" t="n"/>
-      <c r="G11" s="28" t="n"/>
+      <c r="B11" s="34" t="n"/>
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="34" t="n"/>
+      <c r="F11" s="34" t="n"/>
+      <c r="G11" s="35" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="n">
+      <c r="A12" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>Verificar etiquetado y fechas</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C12" s="38" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="39" t="inlineStr">
         <is>
           <t>Sous Chef</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="39" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="15" t="n"/>
+      <c r="F12" s="40" t="n"/>
+      <c r="G12" s="41" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="n">
+      <c r="A13" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t>Reorganizar FIFO</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C13" s="38" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="39" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="39" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="F13" s="40" t="n"/>
+      <c r="G13" s="41" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="29" t="n">
+      <c r="A14" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="37" t="inlineStr">
         <is>
           <t>Retirar producto caducado</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C14" s="38" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="39" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="39" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
-    </row>
-    <row r="15"/>
+      <c r="F14" s="40" t="n"/>
+      <c r="G14" s="41" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="42" t="n"/>
+      <c r="B15" s="42" t="n"/>
+      <c r="C15" s="42" t="n"/>
+      <c r="D15" s="42" t="n"/>
+      <c r="E15" s="42" t="n"/>
+      <c r="F15" s="42" t="n"/>
+      <c r="G15" s="42" t="n"/>
+    </row>
     <row r="16">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">  CONGELADOR</t>
         </is>
       </c>
-      <c r="B16" s="27" t="n"/>
-      <c r="C16" s="27" t="n"/>
-      <c r="D16" s="27" t="n"/>
-      <c r="E16" s="27" t="n"/>
-      <c r="F16" s="27" t="n"/>
-      <c r="G16" s="28" t="n"/>
+      <c r="B16" s="34" t="n"/>
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="34" t="n"/>
+      <c r="E16" s="34" t="n"/>
+      <c r="F16" s="34" t="n"/>
+      <c r="G16" s="35" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="29" t="n">
+      <c r="A17" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="37" t="inlineStr">
         <is>
           <t>Verificar etiquetado y fechas de congelación</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C17" s="38" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="39" t="inlineStr">
         <is>
           <t>Sous Chef</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="39" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="F17" s="40" t="n"/>
+      <c r="G17" s="41" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="29" t="n">
+      <c r="A18" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>Comprobar que no hay producto &gt; 3 meses congelado</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
+        <is>
+          <t>Comprobar que ningún producto supera su vida útil de congelación (ver la tabla al pie de esta hoja)</t>
+        </is>
+      </c>
+      <c r="C18" s="38" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="39" t="inlineStr">
         <is>
           <t>Sous Chef</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="39" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="15" t="n"/>
+      <c r="F18" s="40" t="n"/>
+      <c r="G18" s="41" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="29" t="n">
+      <c r="A19" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Verificar ausencia de quemaduras por frío</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C19" s="38" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="39" t="inlineStr">
         <is>
           <t>Sous Chef</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="39" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="15" t="n"/>
+      <c r="F19" s="40" t="n"/>
+      <c r="G19" s="41" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="n">
+      <c r="A20" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="37" t="inlineStr">
         <is>
           <t>Reorganizar por categoría</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C20" s="38" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="39" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="39" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="15" t="n"/>
-    </row>
-    <row r="21"/>
+      <c r="F20" s="40" t="n"/>
+      <c r="G20" s="41" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="42" t="n"/>
+      <c r="B21" s="42" t="n"/>
+      <c r="C21" s="42" t="n"/>
+      <c r="D21" s="42" t="n"/>
+      <c r="E21" s="42" t="n"/>
+      <c r="F21" s="42" t="n"/>
+      <c r="G21" s="42" t="n"/>
+    </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="A22" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">  ALMACÉN SECO</t>
         </is>
       </c>
-      <c r="B22" s="27" t="n"/>
-      <c r="C22" s="27" t="n"/>
-      <c r="D22" s="27" t="n"/>
-      <c r="E22" s="27" t="n"/>
-      <c r="F22" s="27" t="n"/>
-      <c r="G22" s="28" t="n"/>
+      <c r="B22" s="34" t="n"/>
+      <c r="C22" s="34" t="n"/>
+      <c r="D22" s="34" t="n"/>
+      <c r="E22" s="34" t="n"/>
+      <c r="F22" s="34" t="n"/>
+      <c r="G22" s="35" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="29" t="n">
+      <c r="A23" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="37" t="inlineStr">
         <is>
           <t>Verificar caducidades de conservas y secos</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="C23" s="38" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="39" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="39" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="15" t="n"/>
+      <c r="F23" s="40" t="n"/>
+      <c r="G23" s="41" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="29" t="n">
+      <c r="A24" s="36" t="n">
         <v>13</v>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="37" t="inlineStr">
         <is>
           <t>Reorganizar por fecha: más antiguo delante</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C24" s="38" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D24" s="39" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E24" s="39" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="15" t="n"/>
+      <c r="F24" s="40" t="n"/>
+      <c r="G24" s="41" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="29" t="n">
+      <c r="A25" s="36" t="n">
         <v>14</v>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="37" t="inlineStr">
         <is>
           <t>Verificar ausencia de plagas (polillas, hormigas)</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
+      <c r="C25" s="38" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="39" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E25" s="39" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="15" t="n"/>
+      <c r="F25" s="40" t="n"/>
+      <c r="G25" s="41" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="29" t="n">
+      <c r="A26" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="37" t="inlineStr">
         <is>
           <t>Comprobar envases cerrados y sin humedad</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="C26" s="38" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D26" s="39" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="E26" s="39" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="F26" s="14" t="n"/>
-      <c r="G26" s="15" t="n"/>
-    </row>
-    <row r="27"/>
-    <row r="28"/>
+      <c r="F26" s="40" t="n"/>
+      <c r="G26" s="41" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="43" t="n"/>
+      <c r="B27" s="44" t="n"/>
+      <c r="C27" s="38" t="n"/>
+      <c r="D27" s="39" t="n"/>
+      <c r="E27" s="39" t="n"/>
+      <c r="F27" s="40" t="n"/>
+      <c r="G27" s="41" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="43" t="n"/>
+      <c r="B28" s="44" t="n"/>
+      <c r="C28" s="38" t="n"/>
+      <c r="D28" s="39" t="n"/>
+      <c r="E28" s="39" t="n"/>
+      <c r="F28" s="40" t="n"/>
+      <c r="G28" s="41" t="n"/>
+    </row>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
-        <is>
-          <t>Tareas completadas:</t>
-        </is>
-      </c>
-      <c r="D29" s="16">
-        <f>COUNTIF(F5:F27,"✓")</f>
-        <v>0.0</v>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="F29" s="16">
-        <f>COUNTIF(B5:B27,"?*")</f>
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="30"/>
+      <c r="A29" s="43" t="n"/>
+      <c r="B29" s="44" t="n"/>
+      <c r="C29" s="38" t="n"/>
+      <c r="D29" s="39" t="n"/>
+      <c r="E29" s="39" t="n"/>
+      <c r="F29" s="40" t="n"/>
+      <c r="G29" s="41" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="43" t="n"/>
+      <c r="B30" s="44" t="n"/>
+      <c r="C30" s="38" t="n"/>
+      <c r="D30" s="39" t="n"/>
+      <c r="E30" s="39" t="n"/>
+      <c r="F30" s="40" t="n"/>
+      <c r="G30" s="41" t="n"/>
+    </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>Verificado por:</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="n"/>
-      <c r="C31" s="27" t="n"/>
-      <c r="D31" s="28" t="n"/>
-      <c r="E31" s="16" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="F31" s="15" t="n"/>
-      <c r="G31" s="28" t="n"/>
+      <c r="A31" s="43" t="n"/>
+      <c r="B31" s="44" t="n"/>
+      <c r="C31" s="38" t="n"/>
+      <c r="D31" s="39" t="n"/>
+      <c r="E31" s="39" t="n"/>
+      <c r="F31" s="40" t="n"/>
+      <c r="G31" s="41" t="n"/>
     </row>
     <row r="32"/>
     <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D33" s="16">
+        <f>COUNTIFS(B5:B31,"?*",F5:F31,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F33" s="16">
+        <f>COUNTIF(B5:B31,"?*")-COUNTIF(F5:F31,"N/A")</f>
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>Verificado por:</t>
+        </is>
+      </c>
+      <c r="B35" s="45" t="n"/>
+      <c r="C35" s="27" t="n"/>
+      <c r="D35" s="28" t="n"/>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F35" s="45" t="n"/>
+      <c r="G35" s="28" t="n"/>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="47" t="inlineStr">
+        <is>
+          <t>VIDA ÚTIL ORIENTATIVA EN CONGELACIÓN A −18 °C — ajústala a tu producto y a tu proveedor</t>
+        </is>
+      </c>
+      <c r="B37" s="27" t="n"/>
+      <c r="C37" s="27" t="n"/>
+      <c r="D37" s="27" t="n"/>
+      <c r="E37" s="27" t="n"/>
+      <c r="F37" s="27" t="n"/>
+      <c r="G37" s="28" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n"/>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Familia</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Vida útil</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+      <c r="E38" s="27" t="n"/>
+      <c r="F38" s="27" t="n"/>
+      <c r="G38" s="28" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="47" t="n"/>
+      <c r="B39" s="48" t="inlineStr">
+        <is>
+          <t>Pescado azul y marisco</t>
+        </is>
+      </c>
+      <c r="C39" s="48" t="inlineStr">
+        <is>
+          <t>2-3 meses</t>
+        </is>
+      </c>
+      <c r="D39" s="49" t="inlineStr">
+        <is>
+          <t>La grasa se enrancia aunque esté congelado: es el que antes se estropea</t>
+        </is>
+      </c>
+      <c r="E39" s="27" t="n"/>
+      <c r="F39" s="27" t="n"/>
+      <c r="G39" s="28" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="47" t="n"/>
+      <c r="B40" s="48" t="inlineStr">
+        <is>
+          <t>Pescado blanco</t>
+        </is>
+      </c>
+      <c r="C40" s="48" t="inlineStr">
+        <is>
+          <t>4-6 meses</t>
+        </is>
+      </c>
+      <c r="D40" s="49" t="inlineStr">
+        <is>
+          <t>Entero aguanta menos que en porciones ya limpias y envasadas</t>
+        </is>
+      </c>
+      <c r="E40" s="27" t="n"/>
+      <c r="F40" s="27" t="n"/>
+      <c r="G40" s="28" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="47" t="n"/>
+      <c r="B41" s="48" t="inlineStr">
+        <is>
+          <t>Carne de vacuno y caza</t>
+        </is>
+      </c>
+      <c r="C41" s="48" t="inlineStr">
+        <is>
+          <t>8-12 meses</t>
+        </is>
+      </c>
+      <c r="D41" s="49" t="inlineStr">
+        <is>
+          <t>Piezas enteras; en filetes, la mitad</t>
+        </is>
+      </c>
+      <c r="E41" s="27" t="n"/>
+      <c r="F41" s="27" t="n"/>
+      <c r="G41" s="28" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="47" t="n"/>
+      <c r="B42" s="48" t="inlineStr">
+        <is>
+          <t>Carne de cerdo y cordero</t>
+        </is>
+      </c>
+      <c r="C42" s="48" t="inlineStr">
+        <is>
+          <t>4-6 meses</t>
+        </is>
+      </c>
+      <c r="D42" s="49" t="inlineStr">
+        <is>
+          <t>La grasa de cerdo limita la vida útil</t>
+        </is>
+      </c>
+      <c r="E42" s="27" t="n"/>
+      <c r="F42" s="27" t="n"/>
+      <c r="G42" s="28" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="47" t="n"/>
+      <c r="B43" s="48" t="inlineStr">
+        <is>
+          <t>Aves y conejo</t>
+        </is>
+      </c>
+      <c r="C43" s="48" t="inlineStr">
+        <is>
+          <t>6-9 meses</t>
+        </is>
+      </c>
+      <c r="D43" s="49" t="inlineStr">
+        <is>
+          <t>Enteros; troceados, 6 meses</t>
+        </is>
+      </c>
+      <c r="E43" s="27" t="n"/>
+      <c r="F43" s="27" t="n"/>
+      <c r="G43" s="28" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="47" t="n"/>
+      <c r="B44" s="48" t="inlineStr">
+        <is>
+          <t>Carne picada, hamburguesas y elaborados</t>
+        </is>
+      </c>
+      <c r="C44" s="48" t="inlineStr">
+        <is>
+          <t>2-3 meses</t>
+        </is>
+      </c>
+      <c r="D44" s="49" t="inlineStr">
+        <is>
+          <t>Mucha superficie expuesta: la más delicada</t>
+        </is>
+      </c>
+      <c r="E44" s="27" t="n"/>
+      <c r="F44" s="27" t="n"/>
+      <c r="G44" s="28" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="47" t="n"/>
+      <c r="B45" s="48" t="inlineStr">
+        <is>
+          <t>Pan, masas y bollería</t>
+        </is>
+      </c>
+      <c r="C45" s="48" t="inlineStr">
+        <is>
+          <t>1-3 meses</t>
+        </is>
+      </c>
+      <c r="D45" s="49" t="inlineStr">
+        <is>
+          <t>Pierde textura antes que seguridad</t>
+        </is>
+      </c>
+      <c r="E45" s="27" t="n"/>
+      <c r="F45" s="27" t="n"/>
+      <c r="G45" s="28" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="47" t="n"/>
+      <c r="B46" s="48" t="inlineStr">
+        <is>
+          <t>Verdura escaldada y fruta</t>
+        </is>
+      </c>
+      <c r="C46" s="48" t="inlineStr">
+        <is>
+          <t>8-12 meses</t>
+        </is>
+      </c>
+      <c r="D46" s="49" t="inlineStr">
+        <is>
+          <t>Sin escaldar previamente, la mitad</t>
+        </is>
+      </c>
+      <c r="E46" s="27" t="n"/>
+      <c r="F46" s="27" t="n"/>
+      <c r="G46" s="28" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="47" t="n"/>
+      <c r="B47" s="48" t="inlineStr">
+        <is>
+          <t>Fondos, salsas y caldos propios</t>
+        </is>
+      </c>
+      <c r="C47" s="48" t="inlineStr">
+        <is>
+          <t>3 meses</t>
+        </is>
+      </c>
+      <c r="D47" s="49" t="inlineStr">
+        <is>
+          <t>Etiquetar con fecha de producción Y de congelación: la vida útil de esta tabla se cuenta desde la de congelación</t>
+        </is>
+      </c>
+      <c r="E47" s="27" t="n"/>
+      <c r="F47" s="27" t="n"/>
+      <c r="G47" s="28" t="n"/>
+    </row>
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="18" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="20">
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="D44:G44"/>
+    <mergeCell ref="D47:G47"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="D38:G38"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="B35:D35"/>
     <mergeCell ref="A16:G16"/>
+    <mergeCell ref="D41:G41"/>
+    <mergeCell ref="D46:G46"/>
+    <mergeCell ref="D40:G40"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="D42:G42"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="D39:G39"/>
+    <mergeCell ref="D43:G43"/>
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A22:G22"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G27">
+  <conditionalFormatting sqref="A5:G31">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F17 F18 F19 F20 F23 F24 F25 F26 F27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F17 F18 F19 F20 F23 F24 F25 F26 F27 F28 F29 F30 F31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2021,7 +2633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2043,7 +2655,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable turno: _________________________</t>
+          <t>Mes: ________________   Año: ______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2683,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cadencia</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -2086,490 +2698,1178 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">  EQUIPOS DE COCINA</t>
         </is>
       </c>
-      <c r="B5" s="27" t="n"/>
-      <c r="C5" s="27" t="n"/>
-      <c r="D5" s="27" t="n"/>
-      <c r="E5" s="27" t="n"/>
-      <c r="F5" s="27" t="n"/>
-      <c r="G5" s="28" t="n"/>
+      <c r="B5" s="34" t="n"/>
+      <c r="C5" s="34" t="n"/>
+      <c r="D5" s="34" t="n"/>
+      <c r="E5" s="34" t="n"/>
+      <c r="F5" s="34" t="n"/>
+      <c r="G5" s="35" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="n">
+      <c r="A6" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>Revisión general de horno: resistencias, puerta, juntas</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="38" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="39" t="inlineStr">
         <is>
           <t>Técnico/Chef</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="39" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="F6" s="40" t="n"/>
+      <c r="G6" s="41" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="n">
+      <c r="A7" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>Verificar calibración de termostatos</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="38" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="39" t="inlineStr">
         <is>
           <t>Técnico/Chef</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="39" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="40" t="n"/>
+      <c r="G7" s="41" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="n">
+      <c r="A8" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>Revisión de campana extractora: motor, filtros, conducto</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="38" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="39" t="inlineStr">
         <is>
           <t>Empresa externa</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="39" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="F8" s="40" t="n"/>
+      <c r="G8" s="41" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="n">
+      <c r="A9" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t>Verificar estado de quemadores y pilotos</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="38" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="39" t="inlineStr">
         <is>
           <t>Chef</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="39" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="40" t="n"/>
+      <c r="G9" s="41" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="n">
+      <c r="A10" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="37" t="inlineStr">
         <is>
           <t>Limpiar condensador de cámaras frigoríficas</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="38" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="39" t="inlineStr">
         <is>
           <t>Técnico</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="39" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
+      <c r="F10" s="40" t="n"/>
+      <c r="G10" s="41" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="n">
+      <c r="A11" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="37" t="inlineStr">
         <is>
           <t>Verificar juntas de puertas de cámaras</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="38" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="39" t="inlineStr">
         <is>
           <t>Chef</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="39" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="15" t="n"/>
-    </row>
-    <row r="12"/>
+      <c r="F11" s="40" t="n"/>
+      <c r="G11" s="41" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="37" t="inlineStr">
+        <is>
+          <t>Descalcificar el lavavajillas (frecuencia según la dureza del agua: mensual o trimestral)</t>
+        </is>
+      </c>
+      <c r="C12" s="38" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D12" s="39" t="inlineStr">
+        <is>
+          <t>Técnico/Chef</t>
+        </is>
+      </c>
+      <c r="E12" s="39" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="F12" s="40" t="n"/>
+      <c r="G12" s="41" t="n"/>
+    </row>
     <row r="13">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="A13" s="42" t="n"/>
+      <c r="B13" s="42" t="n"/>
+      <c r="C13" s="42" t="n"/>
+      <c r="D13" s="42" t="n"/>
+      <c r="E13" s="42" t="n"/>
+      <c r="F13" s="42" t="n"/>
+      <c r="G13" s="42" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">  SALA Y BARRA</t>
         </is>
       </c>
-      <c r="B13" s="27" t="n"/>
-      <c r="C13" s="27" t="n"/>
-      <c r="D13" s="27" t="n"/>
-      <c r="E13" s="27" t="n"/>
-      <c r="F13" s="27" t="n"/>
-      <c r="G13" s="28" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="29" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="34" t="n"/>
+      <c r="C14" s="34" t="n"/>
+      <c r="D14" s="34" t="n"/>
+      <c r="E14" s="34" t="n"/>
+      <c r="F14" s="34" t="n"/>
+      <c r="G14" s="35" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="37" t="inlineStr">
         <is>
           <t>Verificar estado del mobiliario: mesas, sillas, bancos</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C15" s="38" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D15" s="39" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E15" s="39" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="29" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="F15" s="40" t="n"/>
+      <c r="G15" s="41" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="36" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="37" t="inlineStr">
         <is>
           <t>Revisar iluminación: bombillas fundidas, focos</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C16" s="38" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D16" s="39" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E16" s="39" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="29" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="F16" s="40" t="n"/>
+      <c r="G16" s="41" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="37" t="inlineStr">
         <is>
           <t>Revisión de climatización: filtros, temperatura</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C17" s="38" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D17" s="39" t="inlineStr">
         <is>
           <t>Técnico</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E17" s="39" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="F17" s="40" t="n"/>
+      <c r="G17" s="41" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="36" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>Verificar estado de TPV y datáfono</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C18" s="38" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D18" s="39" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E18" s="39" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="15" t="n"/>
-    </row>
-    <row r="18"/>
+      <c r="F18" s="40" t="n"/>
+      <c r="G18" s="41" t="n"/>
+    </row>
     <row r="19">
-      <c r="A19" s="24" t="inlineStr">
+      <c r="A19" s="42" t="n"/>
+      <c r="B19" s="42" t="n"/>
+      <c r="C19" s="42" t="n"/>
+      <c r="D19" s="42" t="n"/>
+      <c r="E19" s="42" t="n"/>
+      <c r="F19" s="42" t="n"/>
+      <c r="G19" s="42" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="51" t="inlineStr">
         <is>
           <t xml:space="preserve">  SEGURIDAD</t>
         </is>
       </c>
-      <c r="B19" s="27" t="n"/>
-      <c r="C19" s="27" t="n"/>
-      <c r="D19" s="27" t="n"/>
-      <c r="E19" s="27" t="n"/>
-      <c r="F19" s="27" t="n"/>
-      <c r="G19" s="28" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="29" t="n">
-        <v>11</v>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="34" t="n"/>
+      <c r="C20" s="34" t="n"/>
+      <c r="D20" s="34" t="n"/>
+      <c r="E20" s="34" t="n"/>
+      <c r="F20" s="34" t="n"/>
+      <c r="G20" s="35" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="36" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" s="37" t="inlineStr">
         <is>
           <t>Verificar extintores: carga, accesibilidad, caducidad</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
+      <c r="C21" s="38" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D21" s="39" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E21" s="39" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="15" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="29" t="n">
-        <v>12</v>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="F21" s="40" t="n"/>
+      <c r="G21" s="41" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="36" t="n">
+        <v>13</v>
+      </c>
+      <c r="B22" s="37" t="inlineStr">
         <is>
           <t>Comprobar salidas de emergencia: señalización, acceso libre</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
+      <c r="C22" s="38" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D22" s="39" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E22" s="39" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="15" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="29" t="n">
-        <v>13</v>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="F22" s="40" t="n"/>
+      <c r="G22" s="41" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="36" t="n">
+        <v>14</v>
+      </c>
+      <c r="B23" s="37" t="inlineStr">
         <is>
           <t>Verificar botiquín: stock completo, caducidades</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
+      <c r="C23" s="38" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D23" s="39" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E23" s="39" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="15" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="29" t="n">
-        <v>14</v>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="F23" s="40" t="n"/>
+      <c r="G23" s="41" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="36" t="n">
+        <v>15</v>
+      </c>
+      <c r="B24" s="37" t="inlineStr">
         <is>
           <t>Comprobar detectores de humo</t>
         </is>
       </c>
-      <c r="C23" s="26" t="inlineStr">
+      <c r="C24" s="38" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D24" s="39" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E24" s="39" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="15" t="n"/>
-    </row>
-    <row r="24"/>
-    <row r="25"/>
+      <c r="F24" s="40" t="n"/>
+      <c r="G24" s="41" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="43" t="n"/>
+      <c r="B25" s="44" t="n"/>
+      <c r="C25" s="38" t="n"/>
+      <c r="D25" s="39" t="n"/>
+      <c r="E25" s="39" t="n"/>
+      <c r="F25" s="40" t="n"/>
+      <c r="G25" s="41" t="n"/>
+    </row>
     <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="A26" s="43" t="n"/>
+      <c r="B26" s="44" t="n"/>
+      <c r="C26" s="38" t="n"/>
+      <c r="D26" s="39" t="n"/>
+      <c r="E26" s="39" t="n"/>
+      <c r="F26" s="40" t="n"/>
+      <c r="G26" s="41" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="43" t="n"/>
+      <c r="B27" s="44" t="n"/>
+      <c r="C27" s="38" t="n"/>
+      <c r="D27" s="39" t="n"/>
+      <c r="E27" s="39" t="n"/>
+      <c r="F27" s="40" t="n"/>
+      <c r="G27" s="41" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="43" t="n"/>
+      <c r="B28" s="44" t="n"/>
+      <c r="C28" s="38" t="n"/>
+      <c r="D28" s="39" t="n"/>
+      <c r="E28" s="39" t="n"/>
+      <c r="F28" s="40" t="n"/>
+      <c r="G28" s="41" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="43" t="n"/>
+      <c r="B29" s="44" t="n"/>
+      <c r="C29" s="38" t="n"/>
+      <c r="D29" s="39" t="n"/>
+      <c r="E29" s="39" t="n"/>
+      <c r="F29" s="40" t="n"/>
+      <c r="G29" s="41" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D26" s="16">
-        <f>COUNTIF(F5:F24,"✓")</f>
+      <c r="D31" s="16">
+        <f>COUNTIFS(B5:B29,"?*",F5:F29,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E31" s="17" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F26" s="16">
-        <f>COUNTIF(B5:B24,"?*")</f>
-        <v>14.0</v>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="F31" s="16">
+        <f>COUNTIF(B5:B29,"?*")-COUNTIF(F5:F29,"N/A")</f>
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B28" s="15" t="n"/>
-      <c r="C28" s="27" t="n"/>
-      <c r="D28" s="28" t="n"/>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="B33" s="45" t="n"/>
+      <c r="C33" s="27" t="n"/>
+      <c r="D33" s="28" t="n"/>
+      <c r="E33" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F28" s="15" t="n"/>
-      <c r="G28" s="28" t="n"/>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="F33" s="45" t="n"/>
+      <c r="G33" s="28" t="n"/>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="8">
-    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A20:G20"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="A14:G14"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A31:C31"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G24">
+  <conditionalFormatting sqref="A5:G29">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F20 F21 F22 F23 F24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F21 F22 F23 F24 F25 F26 F27 F28 F29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00795548"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Mantenimiento Trimestral y Anual — Revisiones Contratadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Mes: ________________   Año: ______    Responsable: _________________________</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Nº</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Nº de parte</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Cadencia</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>✓ Completada</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Firma</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CONTRATADO — EMPRESA AUTORIZADA</t>
+        </is>
+      </c>
+      <c r="B5" s="34" t="n"/>
+      <c r="C5" s="34" t="n"/>
+      <c r="D5" s="34" t="n"/>
+      <c r="E5" s="34" t="n"/>
+      <c r="F5" s="34" t="n"/>
+      <c r="G5" s="35" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="37" t="inlineStr">
+        <is>
+          <t>Control de plagas (DDD): visita de la empresa autorizada, parte firmado y certificado en vigor</t>
+        </is>
+      </c>
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="39" t="inlineStr">
+        <is>
+          <t>Empresa DDD</t>
+        </is>
+      </c>
+      <c r="E6" s="39" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="F6" s="40" t="n"/>
+      <c r="G6" s="41" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="37" t="inlineStr">
+        <is>
+          <t>Limpieza de campana y conductos de extracción por empresa homologada</t>
+        </is>
+      </c>
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="39" t="inlineStr">
+        <is>
+          <t>Empresa externa</t>
+        </is>
+      </c>
+      <c r="E7" s="39" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F7" s="40" t="n"/>
+      <c r="G7" s="41" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="37" t="inlineStr">
+        <is>
+          <t>Revisión de extintores y BIE por empresa mantenedora (etiqueta y acta de revisión)</t>
+        </is>
+      </c>
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="39" t="inlineStr">
+        <is>
+          <t>Mantenedor</t>
+        </is>
+      </c>
+      <c r="E8" s="39" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F8" s="40" t="n"/>
+      <c r="G8" s="41" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="37" t="inlineStr">
+        <is>
+          <t>Retimbrado de extintores: prueba de presión cada 5 años desde su fabricación</t>
+        </is>
+      </c>
+      <c r="C9" s="38" t="n"/>
+      <c r="D9" s="39" t="inlineStr">
+        <is>
+          <t>Mantenedor</t>
+        </is>
+      </c>
+      <c r="E9" s="39" t="inlineStr">
+        <is>
+          <t>Cada 5 años</t>
+        </is>
+      </c>
+      <c r="F9" s="40" t="n"/>
+      <c r="G9" s="41" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="37" t="inlineStr">
+        <is>
+          <t>Revisión periódica de la instalación de gas por empresa habilitada</t>
+        </is>
+      </c>
+      <c r="C10" s="38" t="n"/>
+      <c r="D10" s="39" t="inlineStr">
+        <is>
+          <t>Instalador gas</t>
+        </is>
+      </c>
+      <c r="E10" s="39" t="inlineStr">
+        <is>
+          <t>Cada 5 años</t>
+        </is>
+      </c>
+      <c r="F10" s="40" t="n"/>
+      <c r="G10" s="41" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="37" t="inlineStr">
+        <is>
+          <t>Revisión de los equipos de frío por frigorista (estanqueidad y gas refrigerante)</t>
+        </is>
+      </c>
+      <c r="C11" s="38" t="n"/>
+      <c r="D11" s="39" t="inlineStr">
+        <is>
+          <t>Frigorista</t>
+        </is>
+      </c>
+      <c r="E11" s="39" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F11" s="40" t="n"/>
+      <c r="G11" s="41" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="42" t="n"/>
+      <c r="B12" s="42" t="n"/>
+      <c r="C12" s="42" t="n"/>
+      <c r="D12" s="42" t="n"/>
+      <c r="E12" s="42" t="n"/>
+      <c r="F12" s="42" t="n"/>
+      <c r="G12" s="42" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  AGUA, RESIDUOS Y ANALÍTICAS</t>
+        </is>
+      </c>
+      <c r="B13" s="34" t="n"/>
+      <c r="C13" s="34" t="n"/>
+      <c r="D13" s="34" t="n"/>
+      <c r="E13" s="34" t="n"/>
+      <c r="F13" s="34" t="n"/>
+      <c r="G13" s="35" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="37" t="inlineStr">
+        <is>
+          <t>Prevención de legionela si hay torre de refrigeración, spa o agua caliente de riesgo</t>
+        </is>
+      </c>
+      <c r="C14" s="38" t="n"/>
+      <c r="D14" s="39" t="inlineStr">
+        <is>
+          <t>Empresa autorizada</t>
+        </is>
+      </c>
+      <c r="E14" s="39" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F14" s="40" t="n"/>
+      <c r="G14" s="41" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="37" t="inlineStr">
+        <is>
+          <t>Analítica del agua de consumo si el local tiene depósito o captación propia</t>
+        </is>
+      </c>
+      <c r="C15" s="38" t="n"/>
+      <c r="D15" s="39" t="inlineStr">
+        <is>
+          <t>Laboratorio</t>
+        </is>
+      </c>
+      <c r="E15" s="39" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F15" s="40" t="n"/>
+      <c r="G15" s="41" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="36" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="37" t="inlineStr">
+        <is>
+          <t>Retirada de aceite usado por gestor autorizado: archivar los documentos de entrega</t>
+        </is>
+      </c>
+      <c r="C16" s="38" t="n"/>
+      <c r="D16" s="39" t="inlineStr">
+        <is>
+          <t>Gestor autorizado</t>
+        </is>
+      </c>
+      <c r="E16" s="39" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="F16" s="40" t="n"/>
+      <c r="G16" s="41" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="37" t="inlineStr">
+        <is>
+          <t>Revisar el contrato de residuos y el acceso al punto limpio</t>
+        </is>
+      </c>
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="39" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E17" s="39" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F17" s="40" t="n"/>
+      <c r="G17" s="41" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="42" t="n"/>
+      <c r="B18" s="42" t="n"/>
+      <c r="C18" s="42" t="n"/>
+      <c r="D18" s="42" t="n"/>
+      <c r="E18" s="42" t="n"/>
+      <c r="F18" s="42" t="n"/>
+      <c r="G18" s="42" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ADMINISTRACIÓN Y EQUIPOS</t>
+        </is>
+      </c>
+      <c r="B19" s="34" t="n"/>
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="34" t="n"/>
+      <c r="E19" s="34" t="n"/>
+      <c r="F19" s="34" t="n"/>
+      <c r="G19" s="35" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="36" t="n">
+        <v>11</v>
+      </c>
+      <c r="B20" s="37" t="inlineStr">
+        <is>
+          <t>Revisar la póliza del local (continente, contenido y responsabilidad civil) y su vencimiento</t>
+        </is>
+      </c>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="39" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E20" s="39" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F20" s="40" t="n"/>
+      <c r="G20" s="41" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="36" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" s="37" t="inlineStr">
+        <is>
+          <t>Revisión del TPV y del software de facturación (requisitos antifraude / Verifactu)</t>
+        </is>
+      </c>
+      <c r="C21" s="38" t="n"/>
+      <c r="D21" s="39" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E21" s="39" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F21" s="40" t="n"/>
+      <c r="G21" s="41" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="36" t="n">
+        <v>13</v>
+      </c>
+      <c r="B22" s="37" t="inlineStr">
+        <is>
+          <t>Descalcificar la máquina de café y revisar el descalcificador o las resinas (según la dureza del agua)</t>
+        </is>
+      </c>
+      <c r="C22" s="38" t="n"/>
+      <c r="D22" s="39" t="inlineStr">
+        <is>
+          <t>Técnico</t>
+        </is>
+      </c>
+      <c r="E22" s="39" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="F22" s="40" t="n"/>
+      <c r="G22" s="41" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="36" t="n">
+        <v>14</v>
+      </c>
+      <c r="B23" s="37" t="inlineStr">
+        <is>
+          <t>Calibrar los termómetros y las sondas contra un patrón conocido</t>
+        </is>
+      </c>
+      <c r="C23" s="38" t="n"/>
+      <c r="D23" s="39" t="inlineStr">
+        <is>
+          <t>Técnico</t>
+        </is>
+      </c>
+      <c r="E23" s="39" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F23" s="40" t="n"/>
+      <c r="G23" s="41" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="36" t="n">
+        <v>15</v>
+      </c>
+      <c r="B24" s="37" t="inlineStr">
+        <is>
+          <t>Anotar la fecha de la próxima revisión de cada contrato y archivar el parte firmado</t>
+        </is>
+      </c>
+      <c r="C24" s="38" t="n"/>
+      <c r="D24" s="39" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E24" s="39" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="F24" s="40" t="n"/>
+      <c r="G24" s="41" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="43" t="n"/>
+      <c r="B25" s="44" t="n"/>
+      <c r="C25" s="38" t="n"/>
+      <c r="D25" s="39" t="n"/>
+      <c r="E25" s="39" t="n"/>
+      <c r="F25" s="40" t="n"/>
+      <c r="G25" s="41" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="43" t="n"/>
+      <c r="B26" s="44" t="n"/>
+      <c r="C26" s="38" t="n"/>
+      <c r="D26" s="39" t="n"/>
+      <c r="E26" s="39" t="n"/>
+      <c r="F26" s="40" t="n"/>
+      <c r="G26" s="41" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="43" t="n"/>
+      <c r="B27" s="44" t="n"/>
+      <c r="C27" s="38" t="n"/>
+      <c r="D27" s="39" t="n"/>
+      <c r="E27" s="39" t="n"/>
+      <c r="F27" s="40" t="n"/>
+      <c r="G27" s="41" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="43" t="n"/>
+      <c r="B28" s="44" t="n"/>
+      <c r="C28" s="38" t="n"/>
+      <c r="D28" s="39" t="n"/>
+      <c r="E28" s="39" t="n"/>
+      <c r="F28" s="40" t="n"/>
+      <c r="G28" s="41" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="43" t="n"/>
+      <c r="B29" s="44" t="n"/>
+      <c r="C29" s="38" t="n"/>
+      <c r="D29" s="39" t="n"/>
+      <c r="E29" s="39" t="n"/>
+      <c r="F29" s="40" t="n"/>
+      <c r="G29" s="41" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D31" s="16">
+        <f>COUNTIFS(B5:B29,"?*",F5:F29,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F31" s="16">
+        <f>COUNTIF(B5:B29,"?*")-COUNTIF(F5:F29,"N/A")</f>
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>Verificado por:</t>
+        </is>
+      </c>
+      <c r="B33" s="45" t="n"/>
+      <c r="C33" s="27" t="n"/>
+      <c r="D33" s="28" t="n"/>
+      <c r="E33" s="16" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F33" s="45" t="n"/>
+      <c r="G33" s="28" t="n"/>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="8">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A31:C31"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A5:G29">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>

--- a/astro-site/public/dl/kit-tareas/05-tareas-semanales-mensuales.xlsx
+++ b/astro-site/public/dl/kit-tareas/05-tareas-semanales-mensuales.xlsx
@@ -841,6 +841,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="31" t="inlineStr">
         <is>
@@ -848,6 +849,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24" ht="32" customHeight="1">
       <c r="B24" s="32" t="inlineStr">
         <is>
@@ -862,6 +864,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="31" t="inlineStr">
         <is>
@@ -869,6 +872,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29" ht="32" customHeight="1">
       <c r="B29" s="32" t="inlineStr">
         <is>
@@ -883,6 +887,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="31" t="inlineStr">
         <is>
@@ -890,10 +895,11 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="32" customHeight="1">
+    <row r="33"/>
+    <row r="34" ht="16" customHeight="1">
       <c r="B34" s="32" t="inlineStr">
         <is>
-          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día (accesos, luces, clima, terraza).</t>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día.</t>
         </is>
       </c>
     </row>
@@ -911,10 +917,10 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="16" customHeight="1">
+    <row r="37" ht="48" customHeight="1">
       <c r="B37" s="32" t="inlineStr">
         <is>
-          <t>▸ Orden de uso: local → áreas → caja. No se duplican: cada uno cubre un nivel.</t>
+          <t>▸ Orden de uso: local → áreas → caja. Cada fichero cubre un nivel: el de negocio marca el HITO (encender, abrir, cerrar), el de áreas detalla CÓMO se hace en cada zona y el de caja lleva el DINERO. Si una tarea aparece en dos, es a propósito: una es el hito y la otra el detalle.</t>
         </is>
       </c>
     </row>
@@ -925,6 +931,7 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="31" t="inlineStr">
         <is>
@@ -932,6 +939,7 @@
         </is>
       </c>
     </row>
+    <row r="41"/>
     <row r="42" ht="35" customHeight="1">
       <c r="B42" s="31" t="inlineStr">
         <is>
@@ -946,6 +954,7 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="31" t="inlineStr">
         <is>
@@ -1691,7 +1700,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F14 F17 F18 F19 F20 F21 F24 F25 F26 F27 F28 F29 F30 F31 F32" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F14 F17 F18 F19 F20 F21 F24 F25 F26 F27 F28 F29 F30 F31 F32" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2582,25 +2591,25 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="20">
-    <mergeCell ref="F35:G35"/>
     <mergeCell ref="D44:G44"/>
-    <mergeCell ref="D47:G47"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="D38:G38"/>
-    <mergeCell ref="D45:G45"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="D41:G41"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="D47:G47"/>
     <mergeCell ref="D46:G46"/>
     <mergeCell ref="D40:G40"/>
-    <mergeCell ref="A37:G37"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A33:C33"/>
     <mergeCell ref="D42:G42"/>
-    <mergeCell ref="A2:G2"/>
     <mergeCell ref="D39:G39"/>
     <mergeCell ref="D43:G43"/>
-    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A22:G22"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:G31">
@@ -2609,7 +2618,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F17 F18 F19 F20 F23 F24 F25 F26 F27 F28 F29 F30 F31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
+    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F17 F18 F19 F20 F23 F24 F25 F26 F27 F28 F29 F30 F31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3257,8 +3266,8 @@
     <mergeCell ref="A20:G20"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="F33:G33"/>
+    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A2:G2"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A31:C31"/>
@@ -3269,7 +3278,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F21 F22 F23 F24 F25 F26 F27 F28 F29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F21 F22 F23 F24 F25 F26 F27 F28 F29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3869,7 +3878,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
